--- a/SGC-CKN/Excel/61ac980c-13d8-4417-92f2-0c3004778829_Thanh_Hoá_P7-44_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/61ac980c-13d8-4417-92f2-0c3004778829_Thanh_Hoá_P7-44_D800_04-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,11 +98,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">20:00
+    <t xml:space="preserve">02:00
 04/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">22:00
+    <t xml:space="preserve">03:00
 04/04/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">23:50
+    <t xml:space="preserve">03:50
 04/04/2026</t>
   </si>
   <si>
@@ -155,6 +155,10 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">07:15
+04/04/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">08:36
 04/04/2026</t>
   </si>
@@ -182,7 +186,7 @@
     <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">09:04
+    <t xml:space="preserve">09:01
 04/04/2026</t>
   </si>
   <si>
@@ -377,12 +381,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -393,11 +402,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -558,26 +562,26 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1225,19 +1229,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.98</v>
       </c>
       <c r="H11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>3.32</v>
+        <v>6.98</v>
       </c>
       <c r="J11" s="8">
-        <v>1.66</v>
+        <v>6.98</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1266,85 +1270,85 @@
         <v>-8.97</v>
       </c>
       <c r="H12" s="9">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="I12" s="9">
         <v>1.99</v>
       </c>
-      <c r="J12" s="8">
-        <v>1.09</v>
+      <c r="J12" s="12">
+        <v>2.39</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>-8.97</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>-17.3</v>
       </c>
-      <c r="H13" s="12">
-        <v>5.17</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="I13" s="13">
         <v>8.33</v>
       </c>
       <c r="J13" s="8">
-        <v>1.61</v>
-      </c>
-      <c r="K13" s="13" t="s">
+        <v>7.14</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="16">
         <v>-17.3</v>
       </c>
-      <c r="G14" s="15">
-        <v>-24.48</v>
-      </c>
-      <c r="H14" s="15">
+      <c r="G14" s="16">
+        <v>-21.48</v>
+      </c>
+      <c r="H14" s="16">
         <v>0.33</v>
       </c>
-      <c r="I14" s="15">
-        <v>7.18</v>
-      </c>
-      <c r="J14" s="18">
-        <v>21.54</v>
-      </c>
-      <c r="K14" s="16" t="s">
+      <c r="I14" s="16">
+        <v>4.18</v>
+      </c>
+      <c r="J14" s="8">
+        <v>12.54</v>
+      </c>
+      <c r="K14" s="17" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1365,7 +1369,7 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-24.48</v>
+        <v>-21.48</v>
       </c>
       <c r="G15" s="19">
         <v>-26.56</v>
@@ -1374,10 +1378,10 @@
         <v>0.33</v>
       </c>
       <c r="I15" s="19">
-        <v>2.08</v>
-      </c>
-      <c r="J15" s="18">
-        <v>6.24</v>
+        <v>5.08</v>
+      </c>
+      <c r="J15" s="8">
+        <v>15.24</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1394,10 +1398,10 @@
         <v>44</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-26.56</v>
@@ -1406,48 +1410,48 @@
         <v>-36.2</v>
       </c>
       <c r="H16" s="22">
-        <v>2.93</v>
+        <v>1.35</v>
       </c>
       <c r="I16" s="22">
         <v>9.64</v>
       </c>
       <c r="J16" s="8">
-        <v>3.29</v>
+        <v>7.14</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="25">
         <v>-36.2</v>
       </c>
       <c r="G17" s="25">
-        <v>-38.1</v>
+        <v>-38.2</v>
       </c>
       <c r="H17" s="25">
         <v>0.38</v>
       </c>
       <c r="I17" s="25">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J17" s="8">
-        <v>4.96</v>
+        <v>5.22</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1455,69 +1459,69 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.1</v>
+        <v>-38.2</v>
       </c>
       <c r="G18" s="28">
         <v>-39.5</v>
       </c>
       <c r="H18" s="28">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="I18" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="J18" s="18">
-        <v>7.64</v>
+        <v>1.3</v>
+      </c>
+      <c r="J18" s="8">
+        <v>5.57</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" s="31">
         <v>-39.5</v>
       </c>
       <c r="G19" s="31">
-        <v>-45.45</v>
+        <v>-43.45</v>
       </c>
       <c r="H19" s="31">
         <v>1.48</v>
       </c>
       <c r="I19" s="31">
-        <v>5.95</v>
-      </c>
-      <c r="J19" s="8">
-        <v>4.01</v>
+        <v>3.95</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2.66</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1525,34 +1529,34 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" s="34">
-        <v>-45.45</v>
+        <v>-43.45</v>
       </c>
       <c r="G20" s="34">
-        <v>-49</v>
+        <v>-45.03</v>
       </c>
       <c r="H20" s="34">
         <v>0.37</v>
       </c>
       <c r="I20" s="34">
-        <v>3.55</v>
-      </c>
-      <c r="J20" s="18">
-        <v>9.68</v>
+        <v>1.58</v>
+      </c>
+      <c r="J20" s="12">
+        <v>4.31</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1560,7 +1564,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1666,31 +1670,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1707,19 +1711,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.98</v>
       </c>
       <c r="G2" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>3.32</v>
+        <v>6.98</v>
       </c>
       <c r="I2" s="8">
-        <v>1.66</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1742,71 +1746,71 @@
         <v>-8.97</v>
       </c>
       <c r="G3" s="9">
-        <v>1.83</v>
+        <v>0.83</v>
       </c>
       <c r="H3" s="9">
         <v>1.99</v>
       </c>
-      <c r="I3" s="8">
-        <v>1.09</v>
+      <c r="I3" s="12">
+        <v>2.39</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-8.97</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-17.3</v>
       </c>
-      <c r="G4" s="12">
-        <v>5.17</v>
-      </c>
-      <c r="H4" s="12">
+      <c r="G4" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="H4" s="13">
         <v>8.33</v>
       </c>
       <c r="I4" s="8">
-        <v>1.61</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>1</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>-17.3</v>
       </c>
-      <c r="F5" s="15">
-        <v>-24.48</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="F5" s="16">
+        <v>-21.48</v>
+      </c>
+      <c r="G5" s="16">
         <v>0.33</v>
       </c>
-      <c r="H5" s="15">
-        <v>7.18</v>
-      </c>
-      <c r="I5" s="18">
-        <v>21.54</v>
+      <c r="H5" s="16">
+        <v>4.18</v>
+      </c>
+      <c r="I5" s="8">
+        <v>12.54</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1823,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-24.48</v>
+        <v>-21.48</v>
       </c>
       <c r="F6" s="19">
         <v>-26.56</v>
@@ -1832,10 +1836,10 @@
         <v>0.33</v>
       </c>
       <c r="H6" s="19">
-        <v>2.08</v>
-      </c>
-      <c r="I6" s="18">
-        <v>6.24</v>
+        <v>5.08</v>
+      </c>
+      <c r="I6" s="8">
+        <v>15.24</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1858,13 +1862,13 @@
         <v>-36.2</v>
       </c>
       <c r="G7" s="22">
-        <v>2.93</v>
+        <v>1.35</v>
       </c>
       <c r="H7" s="22">
         <v>9.64</v>
       </c>
       <c r="I7" s="8">
-        <v>3.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1875,7 +1879,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1884,16 +1888,16 @@
         <v>-36.2</v>
       </c>
       <c r="F8" s="25">
-        <v>-38.1</v>
+        <v>-38.2</v>
       </c>
       <c r="G8" s="25">
         <v>0.38</v>
       </c>
       <c r="H8" s="25">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I8" s="8">
-        <v>4.96</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1904,25 +1908,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.1</v>
+        <v>-38.2</v>
       </c>
       <c r="F9" s="28">
         <v>-39.5</v>
       </c>
       <c r="G9" s="28">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H9" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="I9" s="18">
-        <v>7.64</v>
+        <v>1.3</v>
+      </c>
+      <c r="I9" s="8">
+        <v>5.57</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1933,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1942,16 +1946,16 @@
         <v>-39.5</v>
       </c>
       <c r="F10" s="31">
-        <v>-45.45</v>
+        <v>-43.45</v>
       </c>
       <c r="G10" s="31">
         <v>1.48</v>
       </c>
       <c r="H10" s="31">
-        <v>5.95</v>
-      </c>
-      <c r="I10" s="8">
-        <v>4.01</v>
+        <v>3.95</v>
+      </c>
+      <c r="I10" s="12">
+        <v>2.66</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1962,30 +1966,30 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-45.45</v>
+        <v>-43.45</v>
       </c>
       <c r="F11" s="34">
-        <v>-49</v>
+        <v>-45.03</v>
       </c>
       <c r="G11" s="34">
         <v>0.37</v>
       </c>
       <c r="H11" s="34">
-        <v>3.55</v>
-      </c>
-      <c r="I11" s="18">
-        <v>9.68</v>
+        <v>1.58</v>
+      </c>
+      <c r="I11" s="12">
+        <v>4.31</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1997,19 +2001,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-49</v>
+        <v>-45.03</v>
       </c>
       <c r="G12" s="39">
-        <v>15.02</v>
+        <v>7.48</v>
       </c>
       <c r="H12" s="39">
-        <v>45.34</v>
+        <v>45.03</v>
       </c>
       <c r="I12" s="39">
-        <v>3.02</v>
+        <v>6.02</v>
       </c>
     </row>
   </sheetData>
